--- a/data/trans_dic/P56$pareja-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$pareja-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -732,32 +732,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,28; 75,44</t>
+          <t>11,31; 76,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,13</t>
+          <t>0,0; 44,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,39</t>
+          <t>0,0; 62,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,63; 54,4</t>
+          <t>12,79; 54,95</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,82</t>
+          <t>0,0; 81,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 55,59</t>
+          <t>7,38; 58,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 44,75</t>
+          <t>5,49; 50,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 87,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 82,95</t>
+          <t>12,54; 80,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,28</t>
+          <t>0,0; 61,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,63; 46,88</t>
+          <t>11,42; 43,02</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 86,63</t>
+          <t>14,76; 86,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,64; 85,98</t>
+          <t>13,52; 86,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,02; 75,98</t>
+          <t>16,7; 79,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,98; 66,16</t>
+          <t>21,1; 64,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,66</t>
+          <t>0,0; 38,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 25,58</t>
+          <t>3,37; 28,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 55,21</t>
+          <t>7,89; 60,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,74; 52,78</t>
+          <t>10,94; 51,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 51,7</t>
+          <t>13,25; 53,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,86; 39,18</t>
+          <t>15,51; 39,22</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,19; 56,62</t>
+          <t>21,93; 54,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,57; 60,12</t>
+          <t>24,87; 57,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,59; 66,85</t>
+          <t>30,01; 66,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,94; 45,81</t>
+          <t>23,55; 43,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,62</t>
+          <t>0,0; 66,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 48,5</t>
+          <t>6,54; 47,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 57,4</t>
+          <t>10,3; 61,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 23,78</t>
+          <t>6,17; 24,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,81; 50,3</t>
+          <t>20,79; 51,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,33; 50,76</t>
+          <t>23,85; 50,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,78; 57,07</t>
+          <t>27,2; 56,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,99; 35,24</t>
+          <t>19,27; 35,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,5; 69,76</t>
+          <t>9,79; 71,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,31; 52,59</t>
+          <t>11,33; 53,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,03; 67,42</t>
+          <t>30,22; 67,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20,31; 51,92</t>
+          <t>20,94; 52,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,32</t>
+          <t>0,0; 41,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 23,74</t>
+          <t>7,6; 25,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 23,1</t>
+          <t>2,47; 23,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 23,54</t>
+          <t>12,14; 23,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,97; 40,25</t>
+          <t>9,55; 42,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,98; 26,31</t>
+          <t>9,93; 26,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,42; 39,4</t>
+          <t>15,9; 37,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,47; 26,5</t>
+          <t>15,26; 26,18</t>
         </is>
       </c>
     </row>
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 18,88</t>
+          <t>4,22; 18,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 23,12</t>
+          <t>7,51; 22,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 22,71</t>
+          <t>7,48; 24,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,88; 18,2</t>
+          <t>8,69; 18,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 18,88</t>
+          <t>4,22; 18,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 23,12</t>
+          <t>7,51; 22,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 22,71</t>
+          <t>7,48; 24,01</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,06; 17,77</t>
+          <t>8,41; 17,53</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,42; 56,12</t>
+          <t>30,1; 57,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,3; 55,11</t>
+          <t>30,14; 55,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,82; 59,55</t>
+          <t>35,47; 57,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,41; 42,19</t>
+          <t>27,31; 42,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 19,31</t>
+          <t>5,82; 19,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,61; 19,89</t>
+          <t>10,09; 20,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,9; 20,93</t>
+          <t>8,54; 21,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,71; 18,29</t>
+          <t>11,75; 18,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,67; 28,44</t>
+          <t>15,68; 28,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,67; 28,46</t>
+          <t>17,36; 27,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19,19; 30,01</t>
+          <t>18,69; 30,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,59; 23,75</t>
+          <t>17,03; 23,75</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>762; 1769</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1942,32 +1942,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>646; 4316</t>
+          <t>647; 4376</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>291; 1274</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1448</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3043</t>
+          <t>0; 2593</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1692; 3043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7091</t>
+          <t>0; 7120</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1575; 6288</t>
+          <t>1478; 6352</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>187; 819</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3921</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>619; 4865</t>
+          <t>646; 5156</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1442</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2165,32 +2165,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2000</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>449; 3628</t>
+          <t>445; 4095</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4066</t>
+          <t>0; 3578</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1260; 8176</t>
+          <t>1236; 7980</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5733</t>
+          <t>0; 5717</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1961; 7904</t>
+          <t>1926; 7253</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>884; 5190</t>
+          <t>884; 5170</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>968; 6099</t>
+          <t>959; 6104</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2401; 7925</t>
+          <t>1742; 8324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3152; 9073</t>
+          <t>2893; 8838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1621</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3962</t>
+          <t>0; 4046</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>737; 4614</t>
+          <t>608; 5171</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>841; 5777</t>
+          <t>825; 6380</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1891; 9297</t>
+          <t>1927; 9149</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2176; 9150</t>
+          <t>2346; 9539</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4719; 12439</t>
+          <t>4924; 12451</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6241; 16679</t>
+          <t>6459; 15971</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10868; 25555</t>
+          <t>10571; 24477</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7544; 16485</t>
+          <t>7400; 16340</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12098; 23153</t>
+          <t>11904; 22178</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4899</t>
+          <t>0; 4876</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1019; 8833</t>
+          <t>1191; 8613</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2233; 12546</t>
+          <t>2251; 13435</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1678; 6702</t>
+          <t>1738; 6853</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7661; 18516</t>
+          <t>7652; 18976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14772; 30825</t>
+          <t>14481; 30566</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11992; 26546</t>
+          <t>12652; 26292</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14952; 27744</t>
+          <t>15167; 27555</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>973; 7147</t>
+          <t>1003; 7307</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2052; 9541</t>
+          <t>2055; 9619</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7967; 17308</t>
+          <t>7757; 17453</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3687; 9423</t>
+          <t>3801; 9570</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6443</t>
+          <t>0; 7166</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5041; 15513</t>
+          <t>4966; 16585</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>899; 8261</t>
+          <t>884; 8565</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9960; 19503</t>
+          <t>10060; 19574</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2468; 11072</t>
+          <t>2628; 11616</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8335; 21965</t>
+          <t>8291; 21853</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10086; 24210</t>
+          <t>9772; 22900</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15621; 26757</t>
+          <t>15412; 26442</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2142; 11317</t>
+          <t>2527; 11075</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7838; 23951</t>
+          <t>7776; 23328</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7208; 21870</t>
+          <t>7207; 23123</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9167; 18782</t>
+          <t>8971; 18735</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2142; 11317</t>
+          <t>2527; 11075</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7838; 23951</t>
+          <t>7776; 23328</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7208; 21870</t>
+          <t>7207; 23123</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9545; 18728</t>
+          <t>8861; 18466</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13721; 27095</t>
+          <t>14530; 27529</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23790; 43266</t>
+          <t>23659; 43177</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26543; 42937</t>
+          <t>25572; 41326</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27145; 41782</t>
+          <t>27041; 42571</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5814; 18067</t>
+          <t>5442; 17941</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19627; 40634</t>
+          <t>20619; 42337</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15173; 35695</t>
+          <t>14574; 36125</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28825; 45023</t>
+          <t>28925; 44983</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22230; 40330</t>
+          <t>22241; 41080</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49970; 80486</t>
+          <t>49100; 78240</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46572; 72838</t>
+          <t>45346; 73766</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>60742; 82005</t>
+          <t>58779; 81979</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$pareja-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$pareja-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 88,28</t>
+          <t>0,0; 86,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,31; 76,48</t>
+          <t>12,48; 80,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,42</t>
+          <t>0,0; 51,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 89,03</t>
+          <t>0,0; 89,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,64</t>
+          <t>0,0; 59,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,79; 54,95</t>
+          <t>14,48; 56,06</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 88,87</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 58,92</t>
+          <t>10,43; 60,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 50,51</t>
+          <t>4,85; 48,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,54; 80,96</t>
+          <t>12,7; 84,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,11</t>
+          <t>0,0; 59,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 43,02</t>
+          <t>12,05; 43,18</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,76; 86,29</t>
+          <t>14,81; 86,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 86,05</t>
+          <t>13,77; 85,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,7; 79,81</t>
+          <t>21,78; 76,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,1; 64,45</t>
+          <t>22,08; 63,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,46</t>
+          <t>0,0; 46,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 28,67</t>
+          <t>4,68; 29,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 60,98</t>
+          <t>7,92; 59,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,94; 51,94</t>
+          <t>10,9; 53,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,25; 53,9</t>
+          <t>9,42; 52,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,51; 39,22</t>
+          <t>16,25; 40,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,93; 54,22</t>
+          <t>21,97; 56,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,87; 57,58</t>
+          <t>26,32; 59,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,01; 66,26</t>
+          <t>30,95; 68,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,55; 43,88</t>
+          <t>22,44; 44,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 47,28</t>
+          <t>5,77; 47,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,3; 61,46</t>
+          <t>14,38; 63,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 24,32</t>
+          <t>6,25; 25,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,79; 51,55</t>
+          <t>20,73; 51,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,85; 50,33</t>
+          <t>23,03; 50,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,2; 56,52</t>
+          <t>27,56; 57,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,27; 35,0</t>
+          <t>19,17; 34,48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 71,33</t>
+          <t>10,17; 67,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,33; 53,01</t>
+          <t>11,43; 52,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,22; 67,98</t>
+          <t>31,92; 69,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20,94; 52,73</t>
+          <t>20,19; 52,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,52</t>
+          <t>0,0; 41,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,6; 25,38</t>
+          <t>6,49; 24,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 23,95</t>
+          <t>2,44; 22,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,14; 23,63</t>
+          <t>12,2; 23,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,55; 42,23</t>
+          <t>7,09; 41,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,93; 26,17</t>
+          <t>10,04; 26,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,9; 37,27</t>
+          <t>15,4; 37,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,26; 26,18</t>
+          <t>14,99; 26,51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,22; 18,48</t>
+          <t>3,99; 19,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,51; 22,51</t>
+          <t>7,73; 22,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,48; 24,01</t>
+          <t>7,76; 23,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,69; 18,15</t>
+          <t>8,8; 18,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,22; 18,48</t>
+          <t>3,99; 19,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,51; 22,51</t>
+          <t>7,73; 22,53</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,48; 24,01</t>
+          <t>7,76; 23,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,41; 17,53</t>
+          <t>8,49; 17,79</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,1; 57,02</t>
+          <t>27,88; 54,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,14; 55,0</t>
+          <t>30,44; 55,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,47; 57,32</t>
+          <t>37,16; 59,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,31; 42,99</t>
+          <t>28,22; 43,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 19,18</t>
+          <t>6,24; 20,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,09; 20,73</t>
+          <t>9,81; 19,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,54; 21,18</t>
+          <t>8,82; 20,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,75; 18,27</t>
+          <t>11,88; 18,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,68; 28,97</t>
+          <t>16,13; 29,62</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,36; 27,67</t>
+          <t>17,65; 27,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,69; 30,4</t>
+          <t>18,75; 30,37</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,03; 23,75</t>
+          <t>17,51; 24,15</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3852</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5724</t>
+          <t>0; 5628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>647; 4376</t>
+          <t>738; 4769</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2593</t>
+          <t>0; 3310</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6662</t>
+          <t>0; 6668</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7120</t>
+          <t>0; 6809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1478; 6352</t>
+          <t>1781; 6894</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4625</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5808</t>
+          <t>0; 6535</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>646; 5156</t>
+          <t>933; 5447</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>445; 4095</t>
+          <t>469; 4646</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1236; 7980</t>
+          <t>1252; 8282</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5717</t>
+          <t>0; 5590</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1926; 7253</t>
+          <t>2244; 8042</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>9275</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>884; 5170</t>
+          <t>887; 5167</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>959; 6104</t>
+          <t>977; 6099</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1742; 8324</t>
+          <t>2272; 7955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2893; 8838</t>
+          <t>3146; 9099</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4046</t>
+          <t>0; 4875</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>608; 5171</t>
+          <t>971; 6147</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>825; 6380</t>
+          <t>829; 6266</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1927; 9149</t>
+          <t>1919; 9420</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2346; 9539</t>
+          <t>1668; 9244</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4924; 12451</t>
+          <t>5686; 14270</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>18293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>22635</t>
         </is>
       </c>
     </row>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6459; 15971</t>
+          <t>6473; 16684</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10571; 24477</t>
+          <t>11189; 25470</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7400; 16340</t>
+          <t>7633; 17004</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11904; 22178</t>
+          <t>12264; 24288</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,37 +2576,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1191; 8613</t>
+          <t>1051; 8597</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2251; 13435</t>
+          <t>3144; 13969</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1738; 6853</t>
+          <t>1882; 7640</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7652; 18976</t>
+          <t>7632; 18910</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14481; 30566</t>
+          <t>13987; 30621</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12652; 26292</t>
+          <t>12820; 26756</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15167; 27555</t>
+          <t>16252; 29237</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>15616</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>22351</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1003; 7307</t>
+          <t>1042; 6867</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2055; 9619</t>
+          <t>2073; 9540</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7757; 17453</t>
+          <t>8194; 17772</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3801; 9570</t>
+          <t>3789; 9880</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7166</t>
+          <t>0; 7111</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4966; 16585</t>
+          <t>4238; 15759</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>884; 8565</t>
+          <t>874; 8152</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10060; 19574</t>
+          <t>10966; 21515</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2628; 11616</t>
+          <t>1950; 11315</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8291; 21853</t>
+          <t>8380; 22245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9772; 22900</t>
+          <t>9462; 22875</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15412; 26442</t>
+          <t>16284; 28794</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>14699</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>14699</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2527; 11075</t>
+          <t>2393; 11545</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7776; 23328</t>
+          <t>8007; 23343</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7207; 23123</t>
+          <t>7468; 23102</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8971; 18735</t>
+          <t>9931; 20741</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2527; 11075</t>
+          <t>2393; 11545</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7776; 23328</t>
+          <t>8007; 23343</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7207; 23123</t>
+          <t>7468; 23102</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8861; 18466</t>
+          <t>9772; 20464</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>36779</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>36341</t>
+          <t>40657</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70816</t>
+          <t>77436</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14530; 27529</t>
+          <t>13462; 26214</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23659; 43177</t>
+          <t>23900; 43723</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25572; 41326</t>
+          <t>26789; 43080</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27041; 42571</t>
+          <t>29557; 45455</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5442; 17941</t>
+          <t>5841; 19438</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20619; 42337</t>
+          <t>20036; 40402</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14574; 36125</t>
+          <t>15047; 35551</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28925; 44983</t>
+          <t>32035; 49821</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22241; 41080</t>
+          <t>22875; 42002</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49100; 78240</t>
+          <t>49912; 79058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45346; 73766</t>
+          <t>45490; 73697</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>58779; 81979</t>
+          <t>65535; 90413</t>
         </is>
       </c>
     </row>
